--- a/rates.xlsx
+++ b/rates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antonfialko/Downloads/suzhou_final_bot_package/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77BF2E5D-35AC-8349-AFC0-0907D574A3E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E8AA06-03C7-8543-9109-710DAADE2085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="37520" windowHeight="20980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="E4" s="6">
         <f>MAX(B6/Controls!$B$6,IF(B8="Да",B5,B9))</f>
-        <v>8.08</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="E6" s="5" t="str">
         <f>IF(E4&lt;=1,"0-1",IF(E4&lt;=5,"1-5",IF(E4&lt;=10,"5-10","&gt;10")))</f>
-        <v>5-10</v>
+        <v>&gt;10</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="E7" s="17">
         <f>IF(E6="0-1",Controls!$B$9,IF(E6="1-5",E4*Controls!$B$10,IF(E6="5-10",E4*Controls!$B$11,E4*Controls!$B$12)))</f>
-        <v>1333.2</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="E9" s="17">
         <f>IF(B12="Да",E4*IFERROR(VLOOKUP(B13,Auto_Delivery_CN!$A$3:$I$200,3,FALSE()),0),0)</f>
-        <v>140.52173913043478</v>
+        <v>175.65217391304347</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="E15" s="18">
         <f>E7+E8+E14</f>
-        <v>1826.3884057971015</v>
+        <v>2008.1884057971015</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="E16" s="17">
         <f>IF(E4&gt;0,E15/E4,"")</f>
-        <v>226.03816903429475</v>
+        <v>198.8305352274358</v>
       </c>
     </row>
     <row r="17" spans="4:5" x14ac:dyDescent="0.2">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="E17" s="17">
         <f>Controls!$B$5</f>
-        <v>149.23076923076923</v>
+        <v>150.76923076923077</v>
       </c>
     </row>
     <row r="18" spans="4:5" x14ac:dyDescent="0.2">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="E18" s="17">
         <f>E4*Controls!$B$5</f>
-        <v>1205.7846153846153</v>
+        <v>1522.7692307692307</v>
       </c>
     </row>
     <row r="19" spans="4:5" x14ac:dyDescent="0.2">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="E19" s="7">
         <f>IF(E18&gt;0,E15/E18-1,"")</f>
-        <v>0.51468876157001642</v>
+        <v>0.31877395814115572</v>
       </c>
     </row>
     <row r="20" spans="4:5" x14ac:dyDescent="0.2">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E20" s="7">
         <f>IF(E7&gt;0,E14/E7,0)</f>
-        <v>0.25741704605243138</v>
+        <v>0.22652700052613961</v>
       </c>
     </row>
     <row r="21" spans="4:5" x14ac:dyDescent="0.2">
@@ -1681,7 +1681,7 @@
         <v>43</v>
       </c>
       <c r="B3" s="9">
-        <v>9700</v>
+        <v>9800</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>44</v>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="B5" s="10">
         <f>B3/B4</f>
-        <v>149.23076923076923</v>
+        <v>150.76923076923077</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>50</v>
@@ -1724,7 +1724,7 @@
         <v>52</v>
       </c>
       <c r="B6" s="9">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>53</v>
@@ -1766,7 +1766,7 @@
         <v>61</v>
       </c>
       <c r="B9" s="9">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>44</v>
@@ -1780,7 +1780,7 @@
         <v>63</v>
       </c>
       <c r="B10" s="9">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>50</v>
@@ -1794,7 +1794,7 @@
         <v>65</v>
       </c>
       <c r="B11" s="9">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>50</v>
@@ -1808,7 +1808,7 @@
         <v>66</v>
       </c>
       <c r="B12" s="9">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>50</v>
@@ -5033,7 +5033,7 @@
       <c r="J3" s="13"/>
       <c r="K3" s="13">
         <f>Controls!$B$9+Controls!$B$8</f>
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="L3" s="13" t="s">
         <v>247</v>
@@ -5070,7 +5070,7 @@
       <c r="J4" s="13"/>
       <c r="K4" s="13">
         <f>3*Controls!$B$10+Controls!$B$8</f>
-        <v>615</v>
+        <v>600</v>
       </c>
       <c r="L4" s="13" t="s">
         <v>249</v>
@@ -5185,7 +5185,7 @@
       <c r="J7" s="13"/>
       <c r="K7" s="13">
         <f>12*Controls!$B$12+Controls!$B$8</f>
-        <v>2130</v>
+        <v>1950</v>
       </c>
       <c r="L7" s="13" t="s">
         <v>253</v>
